--- a/artfynd/A 19598-2023 artfynd.xlsx
+++ b/artfynd/A 19598-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19598-2023 artfynd.xlsx
+++ b/artfynd/A 19598-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89069767</v>
+        <v>91683789</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>639</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Abramsån, Nb</t>
+          <t>Abramsån, mellan Myrträsk och Kvarnforsen, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>802539.0253481846</v>
+        <v>802522</v>
       </c>
       <c r="R2" t="n">
-        <v>7342111.89000693</v>
+        <v>7342090</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-07-31</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,62 +765,57 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sara Elg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Elvira Weibull</t>
+          <t>Sara Elg, Henrik Weibull, Lilian Karlsson, Erik Börjesson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89069769</v>
+        <v>91683794</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97449</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten hornflikmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophozia ascendens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Warnst.) R.M.Schust.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Abramsån, Nb</t>
+          <t>Abramsån, mellan Myrträsk och Kvarnforsen, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>802520.0336515761</v>
+        <v>802560</v>
       </c>
       <c r="R3" t="n">
-        <v>7342097.987693298</v>
+        <v>7342279</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -865,21 +845,11 @@
           <t>2019-07-31</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-31</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,32 +862,32 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Å genom barrskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Murken låga.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sara Elg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Elvira Weibull, Sara Elg, Lilian Karlsson, Erik Börjesson</t>
+          <t>Sara Elg, Henrik Weibull</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89069770</v>
+        <v>91683790</v>
       </c>
       <c r="B4" t="n">
-        <v>92688</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,34 +895,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2387</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Källpraktmossa</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pseudobryum cinclidioides</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Huebener) T.J.Kop.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Abramsån, Nb</t>
+          <t>Abramsån, mellan Myrträsk och Kvarnforsen, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802516.2726209692</v>
+        <v>802522</v>
       </c>
       <c r="R4" t="n">
-        <v>7342091.037529938</v>
+        <v>7342075</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -982,19 +952,9 @@
           <t>2019-07-31</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-07-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,49 +974,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Sara Elg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henrik Weibull, Elvira Weibull</t>
+          <t>Sara Elg, Henrik Weibull</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>91683791</v>
+        <v>91683792</v>
       </c>
       <c r="B5" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1066,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802522.0431524883</v>
+        <v>802530</v>
       </c>
       <c r="R5" t="n">
-        <v>7342083.063149176</v>
+        <v>7342079</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,19 +1054,9 @@
           <t>2019-07-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-07-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,37 +1088,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>91683789</v>
+        <v>91685630</v>
       </c>
       <c r="B6" t="n">
-        <v>77577</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>639</v>
+        <v>1841</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Vedflikmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Lophozia guttulata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(Lindb. &amp; Arnell) A.Evans</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>802522.1159199576</v>
+        <v>802543</v>
       </c>
       <c r="R6" t="n">
-        <v>7342090.027155528</v>
+        <v>7342285</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,19 +1156,9 @@
           <t>2019-07-31</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-07-31</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,22 +1183,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Sara Elg, Henrik Weibull, Lilian Karlsson, Erik Börjesson</t>
+          <t>Lilian Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>91683792</v>
+        <v>89069758</v>
       </c>
       <c r="B7" t="n">
-        <v>98493</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1365</v>
+        <v>2387</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Abramsån, mellan Myrträsk och Kvarnforsen, Nb</t>
+          <t>Abramsån, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>802530.2583514522</v>
+        <v>802591</v>
       </c>
       <c r="R7" t="n">
-        <v>7342079.033526991</v>
+        <v>7342268</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1333,19 +1258,14 @@
           <t>2019-07-31</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-07-31</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stenblocksträng med stockar under</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1365,27 +1285,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Sara Elg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Sara Elg, Henrik Weibull</t>
+          <t>Henrik Weibull, Elvira Weibull</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91683790</v>
+        <v>89069770</v>
       </c>
       <c r="B8" t="n">
-        <v>98493</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1393,34 +1308,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1365</v>
+        <v>2387</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Abramsån, mellan Myrträsk och Kvarnforsen, Nb</t>
+          <t>Abramsån, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>802522.1004783747</v>
+        <v>802516</v>
       </c>
       <c r="R8" t="n">
-        <v>7342074.885501307</v>
+        <v>7342091</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1450,19 +1365,9 @@
           <t>2019-07-31</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-07-31</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1482,15 +1387,423 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Henrik Weibull, Elvira Weibull</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>91683695</v>
+      </c>
+      <c r="B9" t="n">
+        <v>95962</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>2387</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Källpraktmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pseudobryum cinclidioides</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Huebener) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Abramsån, mellan Myrträsk och Kvarnforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>802593</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7342252</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-07-31</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-07-31</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Å genom barrskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Sara Elg</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Sara Elg, Henrik Weibull</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>91685564</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97231</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Abramsån, mellan Myrträsk och Kvarnforsen, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>802543</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7342285</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2019-07-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2019-07-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Å genom barrskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sara Elg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lilian Karlsson, Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>89069767</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Abramsån, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>802539</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7342112</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-07-31</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-07-31</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Å genom barrskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Henrik Weibull, Elvira Weibull</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>89069769</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Abramsån, Nb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>802520</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7342098</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Råneå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2019-07-31</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2019-07-31</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Å genom barrskog med lövinslag</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Weibull, Elvira Weibull, Sara Elg, Lilian Karlsson, Erik Börjesson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19598-2023 artfynd.xlsx
+++ b/artfynd/A 19598-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91683789</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91683794</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91683790</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91683792</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,6 +1212,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91685630</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89069758</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1396,6 +1431,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89069770</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91683695</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1600,6 +1645,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/91685564</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89069767</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,8 +1859,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89069769</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>